--- a/public/templates/000_pm_suite/01_프로젝트 관리/07_의사소통관리/00_회의록/프로젝트명_회의록.xlsx
+++ b/public/templates/000_pm_suite/01_프로젝트 관리/07_의사소통관리/00_회의록/프로젝트명_회의록.xlsx
@@ -55,7 +55,7 @@
     <t>Commentator</t>
   </si>
   <si>
-    <t>ⓒ Fixframe Inc. All rights reserved.</t>
+    <t>ⓒ Empasy Inc. All rights reserved.</t>
   </si>
 </sst>
 </file>

--- a/public/templates/000_pm_suite/01_프로젝트 관리/07_의사소통관리/00_회의록/프로젝트명_회의록.xlsx
+++ b/public/templates/000_pm_suite/01_프로젝트 관리/07_의사소통관리/00_회의록/프로젝트명_회의록.xlsx
@@ -519,7 +519,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[PM-18] SyncGuard AI 프로젝트 주간·기술검토 통합 회의록 관리대장 — 주식회사 한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>[PM-18] SyncFlow AI 프로젝트 주간·기술검토 통합 회의록 관리대장 — 주식회사 한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>기간계(ProductLab·MarketingHub) 연계 협의</t>
+          <t>기간계(PLM-Nexus·SRM-Portal) 연계 협의</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>ProductLab 전성분은 매일 02:00 읽기전용 뷰 일배치 동기화로 확정</t>
+          <t>PLM-Nexus 자재BOM은 매일 02:00 읽기전용 뷰 일배치 동기화로 확정</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>요구사항 61건 확정(Scope Freeze) 심의</t>
+          <t>요구사항 61건 확정(Scope Freeze) 검증</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>영문 수출 문안 심의 룰셋 추가(CR-2026-003) 협의</t>
+          <t>영문 수출 계약조항 검증 룰셋 추가(CR-2026-003) 협의</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>영문 금지어 20개 패턴 추가를 저우선순위 통계 차트 1종과 무상 상계(Swap) 합의</t>
+          <t>영문 독소조항 20개 패턴 추가를 저우선순위 통계 차트 1종과 무상 상계(Swap) 합의</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
